--- a/database/Courses.xlsx
+++ b/database/Courses.xlsx
@@ -5,17 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Course-management\Document\Database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Course-management\Document\Database\Courses\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2A1DEA7-0EB1-49D8-BBD9-64C94A813111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955A42F3-2DF1-4CE0-840A-18F4AD3F693B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TBL_COURSE" sheetId="1" r:id="rId1"/>
     <sheet name="TBL_CATEGORY" sheetId="2" r:id="rId2"/>
     <sheet name="TBL_LEVEL" sheetId="3" r:id="rId3"/>
+    <sheet name="TBL_LANGUAGE" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="30">
   <si>
     <t>No</t>
   </si>
@@ -966,4 +967,137 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05DF1080-4ED5-43C9-8701-54E90CD17413}">
+  <dimension ref="A2:E9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>